--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,6 +374,9 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
@@ -381,53 +384,53 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:documentId</t>
-  </si>
-  <si>
-    <t>documentId</t>
-  </si>
-  <si>
-    <t>Identifiant du document dont est issu la donnée, par exemple le CR-Bio dont est issu une glycémie.</t>
-  </si>
-  <si>
-    <t>Extension.extension:documentId.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:documentId.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:documentId.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:documentId.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
+    <t>Extension.extension:originalCode</t>
+  </si>
+  <si>
+    <t>originalCode</t>
+  </si>
+  <si>
+    <t>Code original de la donnée. Il permet notamment d'identifier le niveau de comparabilité des résultats entre eux. Le choix a été fait de ne pas indiquer directement le numéro de comparabilité mais d'indiquer directement le code LOINC d'origine pour identifier le numéro de comparabilité dans le jeu de valeur circuit de la biologie.</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalCode.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalCode.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalCode.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Extension.extension:originalCode</t>
-  </si>
-  <si>
-    <t>originalCode</t>
-  </si>
-  <si>
-    <t>Code original de la donnée. Il permet notamment d'identifier le niveau de comparabilité des résultats entre eux. Le choix a été fait de ne pas indiquer directement le numéro de comparabilité mais d'indiquer directement le code LOINC d'origine pour identifier le numéro de comparabilité dans le jeu de valeur circuit de la biologie.</t>
-  </si>
-  <si>
-    <t>Extension.extension:originalCode.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:originalCode.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:originalCode.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:originalCode.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>Extension.extension:originalValue</t>
+  </si>
+  <si>
+    <t>originalValue</t>
+  </si>
+  <si>
+    <t>Valeur originale | Original value</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalValue.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalValue.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalValue.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:originalValue.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
 </t>
   </si>
   <si>
@@ -1667,7 +1670,7 @@
         <v>76</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="T9" t="s" s="2">
         <v>76</v>
@@ -1706,7 +1709,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1718,7 +1721,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>111</v>
@@ -1726,13 +1729,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1757,7 +1760,7 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M10" t="s" s="2">
         <v>92</v>
@@ -1831,7 +1834,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>101</v>
@@ -1934,7 +1937,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>103</v>
@@ -2037,7 +2040,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>105</v>
@@ -2080,7 +2083,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>76</v>
@@ -2142,7 +2145,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>113</v>
@@ -2168,7 +2171,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>115</v>
@@ -2225,7 +2228,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2237,7 +2240,7 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>111</v>
@@ -2245,13 +2248,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
@@ -2276,7 +2279,7 @@
         <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>92</v>
@@ -2350,7 +2353,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>101</v>
@@ -2453,7 +2456,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>103</v>
@@ -2556,7 +2559,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>105</v>
@@ -2599,7 +2602,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>76</v>
@@ -2661,7 +2664,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>113</v>
@@ -2687,7 +2690,7 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>115</v>
@@ -2744,7 +2747,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -2756,7 +2759,7 @@
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>111</v>
@@ -2869,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2895,7 +2898,7 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>115</v>
@@ -2952,7 +2955,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -2964,7 +2967,7 @@
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>111</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-origin-of-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
